--- a/public/assets/documents/excel/sample_upload/first_aid_location.xlsx
+++ b/public/assets/documents/excel/sample_upload/first_aid_location.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deveopers\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Xampp\82\htdocs\NeoEHS_Karam\public\assets\documents\excel\sample_upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,16 +30,16 @@
     <t>Department Name</t>
   </si>
   <si>
-    <t>Excat Location</t>
-  </si>
-  <si>
-    <t>Station Master</t>
-  </si>
-  <si>
     <t>Station Number</t>
   </si>
   <si>
     <t>First Aid Box Number</t>
+  </si>
+  <si>
+    <t>Exact Location</t>
+  </si>
+  <si>
+    <t>Station Master (Employee / Worker Name)</t>
   </si>
 </sst>
 </file>
@@ -377,16 +377,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
